--- a/Automotive Data Solutions/manual_risk_events.xlsx
+++ b/Automotive Data Solutions/manual_risk_events.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA209"/>
+  <dimension ref="A1:AA274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -24858,6 +24858,6396 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>mcs2026-aluminum-us-section232-tariffs</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>TARIFF</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>section_232</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>US imposes 25% Section 232 tariff on aluminum imports; doubled to 50% by June 2025</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>In March 2025 the United States imposed a 25% tariff on aluminum and aluminum derivative products under Section 232 of the Trade Expansion Act, ending all previously existing country-specific exemptions. By June 2025 the tariff was doubled to 50% ad valorem for most countries (the United Kingdom remained at 25%), and in August 2025 more than 400 additional aluminum-related tariff codes were added, with the tariffs applying only to the aluminum content of those products.</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>geopolitical</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Aluminum chapter — Events, Trends, and Issues (pp. 40-41)</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Month precision only (source states In March / By June / In August). Likely overlaps GTA/FR rows — duplicate hints expected.</t>
+        </is>
+      </c>
+      <c r="W210" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>event_id=21461; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>21461</t>
+        </is>
+      </c>
+      <c r="Z210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>mcs2026-cobalt-drc-export-quota-regime</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>national_export_quota</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>DRC replaces cobalt export ban with quotas: 18,125 t rest-2025; 96,600 t/yr 2026-27</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Congo (Kinshasa), an estimated 73% of world mined cobalt in 2025, temporarily banned cobalt exports in February 2025 to address market oversupply and low prices. In October 2025 the ban was replaced with export quotas of 18,125 tons of contained cobalt for the remainder of 2025 and up to 96,600 tons of contained cobalt per year in 2026 and 2027, inclusive of 9,600 tons for national strategic reserves. USGS notes supply uncertainty after the ban announcement likely contributed to the sharp increase in estimated US imports and industry stocks during the year.</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Cobalt chapter — Events, Trends, and Issues (pp. 70-71)</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Quantified quota update to DRC_COBALT_QUOTA_2025 + existing GTA rows — expect duplicate hints; the value here is the USGS-cited tonnages.</t>
+        </is>
+      </c>
+      <c r="W211" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>event_id=21462; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="Z211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>mcs2026-cobalt-us-nds-solicitation-cancelled</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>stockpile_procurement</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>US National Defense Stockpile cobalt solicitation (7,480 t over 5 years) cancelled</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>In 2025 the United States published a solicitation to procure 7,480 tons of cobalt over a period of 5 years for the National Defense Stockpile. The solicitation was cancelled before the end of the year.</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>geopolitical</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Cobalt chapter — Events, Trends, and Issues (pp. 70-71)</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Year precision. Demand-side signal; display-only candidate.</t>
+        </is>
+      </c>
+      <c r="W212" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>event_id=21463; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>21463</t>
+        </is>
+      </c>
+      <c r="Z212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>mcs2026-copper-us-production-disruptions</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>production_curtailment</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>US copper output hit by concentrator shutdowns and lower grades; refined production -9%</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>In 2025, US copper production was affected by concentrator shutdowns and lower ore grades at multiple mines. Domestic refined copper output decreased by an estimated 9% from 2024 owing to planned maintenance at both primary smelters. The COMEX price was projected to average a record $4.80/lb (+14% vs 2024), attributed primarily to uncertainty over tariffs on US copper imports.</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Copper chapter — Events, Trends, and Issues (pp. 72-73)</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Year-aggregate event. Partially offset by 2025 startups: new Arizona mine, secondary smelter (GA), secondary refinery (KY).</t>
+        </is>
+      </c>
+      <c r="W213" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>event_id=21464; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>21464</t>
+        </is>
+      </c>
+      <c r="Z213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>mcs2026-us-critical-minerals-list-2025</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>REGULATORY_COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>critical_minerals_designation</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>US Final 2025 Critical Minerals List adds copper, phosphate rock, silicon, silver, others</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>The US Final 2025 List of Critical Minerals was published in the Federal Register on November 7, 2025 (90 FR 50494). Changes from the 2022 list added copper, lead, potash, rhenium, silicon, and silver under USGS's updated methodology; based on public comment and interagency input on the draft list (90 FR 41591), boron, metallurgical coal, phosphate rock, and uranium were also added.</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>regulatory_compliance</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Copper; Phosphate</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Copper chapter — Events, Trends, and Issues (pp. 72-73)</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>FR-canonical (90 FR 50494) — FR ingester may already carry this; duplicate hints expected. Materials limited to launch list; full additions in summary.</t>
+        </is>
+      </c>
+      <c r="W214" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>event_id=21465; mat=2; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>21465</t>
+        </is>
+      </c>
+      <c r="Z214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>mcs2026-graphite-us-adcvd-china-aam</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>TARIFF</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>anti_dumping_countervailing</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>US sets preliminary AD duty 93.50% and CVD up to 721.03% on Chinese graphite anode material</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Following a December 2024 petition by North American graphite producers, the ITC determined that graphite active anode material (AAM) from China was likely being sold at less than fair value in the United States. In 2025 the Department of Commerce released preliminary results setting antidumping duties at 93.50% and countervailing duties from 11.58% to 721.03% depending on company. US imports of graphite battery anode material (natural + synthetic) in the first 8 months of 2025 were 43,400 t vs 28,100 t a year earlier — led by China (55%), Indonesia (31%), Korea (14%).</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>geopolitical</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Natural Graphite</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Graphite (Natural) chapter — Events, Trends, and Issues (pp. 92-93)</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Year precision on the preliminary determinations. FR AD/CVD procedural steps route display_only by policy; this row aggregates the determinations with duty rates — triage decides. 2026-08-18 UPDATE: largely superseded - per GCMO 2026 p.167, total US tariffs on Chinese graphite fell from &gt;200% (Feb 2026) to ~35% by late March 2026 after Supreme Court and USITC rulings. Adjudicate together with gcmo2026-graphite-us-tariff-collapse at triage.</t>
+        </is>
+      </c>
+      <c r="W215" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>event_id=21466; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>21466</t>
+        </is>
+      </c>
+      <c r="Z215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>mcs2026-graphite-balama-suspension-restart</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>mine_suspension</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Balama graphite mine (Mozambique) restarts June 2025 after suspension since late 2024</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>An Australian company restarted production at the Balama Mine in Mozambique in June 2025, after operations had been suspended since late 2024. USGS does not name the operator; Balama is operated by Syrah Resources.</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Syrah Resources</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Natural Graphite</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Graphite (Natural) chapter — Events, Trends, and Issues (pp. 92-93)</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Restoration event; the underlying late-2024 suspension may already be in corpus via the Syrah walkthrough — check at triage.</t>
+        </is>
+      </c>
+      <c r="W216" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>event_id=21467; mat=1; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>21467</t>
+        </is>
+      </c>
+      <c r="Z216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>mcs2026-ironore-minnesota-idlings</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>mine_idling</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Two Minnesota iron ore mines idled (combined 10 Mt/y capacity); US output -16% in 2025</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>In March 2025 the operating company idled two Minnesota iron ore mines — one indefinitely and one partially — with a combined rated capacity of 10 million tons per year, as part of a strategy to decrease stockpiles. US iron ore production was estimated at 38 million tons in 2025, a 16% decrease from 45.1 million tons in 2024.</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Iron Ore</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Iron Ore chapter — Events, Trends, and Issues (pp. 108-109)</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>USGS does not name the operator. Month precision.</t>
+        </is>
+      </c>
+      <c r="W217" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>event_id=21468; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>21468</t>
+        </is>
+      </c>
+      <c r="Z217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>mcs2026-lithium-namibia-production-halt</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>legal_uncertainty</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Namibia temporarily removed from lithium mine production owing to legal uncertainties</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>USGS reports Namibia was temporarily removed from world lithium mine production in 2025 owing to legal uncertainties. Separately, some producers reduced output or postponed expansion projects in 2025 owing to low prices, while significant capacity expansions proceeded in Argentina, Brazil, Canada, Chile, China, Mali, the US, and Zimbabwe.</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Lithium chapter — Events, Trends, and Issues (pp. 118-119)</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Year precision; no operator named. primary_country NA = Namibia (ISO2).</t>
+        </is>
+      </c>
+      <c r="W218" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>event_id=21469; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>21469</t>
+        </is>
+      </c>
+      <c r="Z218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>mcs2026-manganese-gemco-resumption</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>weather_event</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Northern Australia manganese mine resumes May 2025 after 2024 cyclone suspension</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>A manganese mine in northern Australia that suspended operations in 2024 owing to a tropical cyclone resumed operation in May 2025. USGS does not name the operation; the Groote Eylandt (GEMCO) operation is South32's. 2025 YTD average spot prices for 44%-grade manganese ore from China were down 22% vs the 2024 annual average.</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>South32</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Manganese</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Manganese chapter — Events, Trends, and Issues (pp. 124-125)</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Restoration closing the 2024 cyclone disruption (likely already in corpus via the South32 walkthrough). 2026-08-18 UPDATE from GCMO 2026 p.189: operations paused AGAIN in March 2026 by a new cyclone (see gcmo2026-manganese-gemco-cyclone-repause). NOTE source discrepancy: USGS MCS says resumed May 2025; IEA says 'resuming production in 2026' - adjudicate.</t>
+        </is>
+      </c>
+      <c r="W219" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>event_id=21470; mat=1; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>21470</t>
+        </is>
+      </c>
+      <c r="Z219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>mcs2026-nickel-eo14285-seabed-minerals</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>executive_order</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>US EO 14285 directs seabed mineral development for nickel and other critical minerals</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Executive Order 14285, issued in April 2025, called for development of seabed mineral deposits to help secure supplies of critical minerals such as nickel; several companies subsequently submitted applications to explore regions prospective for nickel-bearing ferromanganese crusts and polymetallic nodules. A 2022 USGS study estimated global seabed deposits contain approximately 4.5 billion tons of nickel.</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>geopolitical</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Nickel; Cobalt</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Nickel chapter — Events, Trends, and Issues (pp. 132-133)</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Supportive/neutral direction — display-only candidate.</t>
+        </is>
+      </c>
+      <c r="W220" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>event_id=21471; mat=2; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>21471</t>
+        </is>
+      </c>
+      <c r="Z220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>mcs2026-ree-china-export-controls-april</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>export_licensing</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>China adds Sm, Gd, Tb, Dy, Lu, Sc, Y alloys/compounds/metals/oxides to export controls</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>In April 2025 China tightened its rare-earth export controls, adding specific controls on alloys, compounds, metals, and oxides of samarium, gadolinium, terbium, dysprosium, lutetium, scandium, and yttrium, and their related products. China began issuing general export licenses to selected exporters. Impact (GCMO 2026): export volumes from China dropped sharply in April and May 2025, leaving many automakers in the United States, Europe and beyond struggling to source permanent magnets; dysprosium and terbium oxide and metal exports fell before slowly recovering, and a significant premium for magnets produced outside China persisted even after trade volumes recovered.</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements; Dysprosium; Terbium</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Rare Earths chapter — Events, Trends, and Issues (pp. 152-153)</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Almost certainly duplicates GTA/IEA rows + CN_REE_EXPORT_2025 regulation — confirm as duplicate or merge at triage; USGS citation adds authority. 2026-08-18 UPDATE from GCMO 2026 pp.174-175: added measured impact (Apr/May export drop, automaker sourcing struggles, Dy/Tb export dip, ex-China magnet premium).</t>
+        </is>
+      </c>
+      <c r="W221" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>event_id=21472; mat=3; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>21472</t>
+        </is>
+      </c>
+      <c r="Z221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>mcs2026-ree-china-controls-oct-expansion-nov-suspension</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>export_licensing</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>China expands REE export controls in October 2025, suspends the expansion for one year in November</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>In October 2025 China expanded rare-earth export controls to include europium, holmium, erbium, thulium, and ytterbium - holmium notably because magnet makers had adopted it as a substitute after the April controls - and broadened the scope to cover internationally made products containing Chinese-sourced parts, components and assemblies, or manufactured using Chinese technologies. In November 2025 China suspended the October measures for one year; the April 2025 controls remained in effect, with general export licences issued to selected exporters. Market context (GCMO 2026): NdPr oxide prices nearly doubled over the seven months from October 2025, reaching ~USD 125/kg in February 2026, their highest since mid-2022.</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>geopolitical</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Rare Earths chapter — Events, Trends, and Issues (pp. 152-153)</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Severity reflects the November one-year suspension of the October expansion (April controls still binding) — captured in one row precisely to avoid the suspended-measure severity trap from the GTA audit. 2026-08-18 UPDATE from GCMO 2026 p.175: added extraterritorial scope (internationally-made products with Chinese content/technology), holmium-substitution driver, NdPr price context; severity 0.55-&gt;0.60. 2026-08-18: exact dates per GCMO p.42: announced 9 Oct 2025; the 'internationally made' licence requirement was to take effect 1 Dec 2025; Jan 2026 China separately tightened dual-use export controls destined for Japan.</t>
+        </is>
+      </c>
+      <c r="W222" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>event_id=21473; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>21473</t>
+        </is>
+      </c>
+      <c r="Z222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>gcmo2026-lithium-zimbabwe-ore-export-ban</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>export_ban</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Zimbabwe suspends lithium concentrate exports (Feb 2026), with potential full export ban in 2027</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Per GCMO 2026 (export controls table p.39 and lithium chapter p.140): Zimbabwe suspended exports of lithium concentrate in February 2026, to be followed by a potential export ban in 2027. IEA attributes part of the early-2026 lithium price rebound (carbonate back above USD 20,000/t LCE) to the tightening of upstream supply from Zimbabwe's measures, alongside tighter Jiangxi permitting and downstream restocking. Zimbabwe holds ~10% of lithium mining share.</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>ZW</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Outlook for lithium — p. 140</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Year precision. Corroborates existing ZW_LITHIUM_EXPORT_BAN regulation + GTA rows — expect duplicate hints; value is the IEA-cited market impact. 2026-08-18 CORRECTED from p.39 table: measure is a Feb 2026 concentrate-export suspension + potential 2027 ban (was year-2025 anchored). Reconcile with ZW_LITHIUM_EXPORT_BAN regulation (2025-announced, Jan 2027 effective) at triage - same policy arc.</t>
+        </is>
+      </c>
+      <c r="W223" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>event_id=21474; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>21474</t>
+        </is>
+      </c>
+      <c r="Z223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>gcmo2026-lithium-jiangxi-permitting-tightening</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>REGULATORY_COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>permitting_restriction</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Tighter permitting in China's Jiangxi lepidolite region constrains lithium supply</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>IEA cites tighter permitting in China's Jiangxi region (the lepidolite mining hub) as a driver of tightening upstream lithium supply conditions contributing to the early-2026 price recovery. A resumption of lepidolite mining in China is flagged as a principal downside risk to prices.</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>regulatory_compliance; operational</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Outlook for lithium — p. 140</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Year precision; IEA names no specific measure or operator.</t>
+        </is>
+      </c>
+      <c r="W224" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>event_id=21475; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>21475</t>
+        </is>
+      </c>
+      <c r="Z224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>gcmo2026-lithium-kemerton-curtailment</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>production_curtailment</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Hydroxide weakness drives curtailments at Australia's Kemerton lithium plant</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Weak lithium hydroxide demand relative to carbonate (driven by the rise of LFP chemistries) continued to weigh on hydroxide refineries in 2025, leading to curtailments outside China including at Australia's Kemerton plant. IEA does not name the operator; Kemerton is Albemarle's. IEA separately notes a possible Kemerton restart could support renewed Australian refining growth.</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Albemarle Corporation</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Outlook for lithium — p. 142</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Year precision. May already be in corpus via the Albemarle walkthrough — check at triage.</t>
+        </is>
+      </c>
+      <c r="W225" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>event_id=21476; mat=1; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>21476</t>
+        </is>
+      </c>
+      <c r="Z225" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>gcmo2026-lithium-keliber-start</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Finland's Keliber lithium mine begins operating — first significant EU hard-rock supply</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Finland's Keliber mine began operating in 2025, with a planned annual capacity of 2.5 kt Li before 2030 — sufficient, per IEA, to meet about 90% of European demand for cathode production in the short term. France is also accelerating the Allier hard-rock and Alsace brine projects.</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>material_concentration; operational</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Outlook for lithium — p. 141</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Positive supply-diversification event — display_only candidate (POSITIVE_DEVELOPMENT subtype cannot be promoted to scoring). Typed CAPACITY_CHANGE (type added 2026-08-17).</t>
+        </is>
+      </c>
+      <c r="W226" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>event_id=21477; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>21477</t>
+        </is>
+      </c>
+      <c r="Z226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>gcmo2026-lithium-huayou-zimbabwe-refinery</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Africa's first lithium refinery ramps up: Huayou's USD 400M Zimbabwe sulphate plant</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>The first half of 2026 was marked by the start of the first lithium refining plant in Africa: the ramp-up of a China-owned Zhejiang Huayou factory in Zimbabwe, a USD 400 million investment designed to refine about 6.5 kt Li as sulphate for further overseas conversion. Diversifies refining geography but extends Chinese ownership — IEA notes over 65% of new African lithium mining capacity is owned by China-headquartered companies.</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>material_concentration</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>ZW</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Outlook for lithium — p. 142</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>H1-2026 precision. Positive/structural — display_only candidate; China-ownership nuance recorded for the concentration narrative. Typed CAPACITY_CHANGE (type added 2026-08-17).</t>
+        </is>
+      </c>
+      <c r="W227" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>event_id=21478; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>21478</t>
+        </is>
+      </c>
+      <c r="Z227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>gcmo2026-nickel-indonesia-rkab-revision</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>production_quota</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Indonesia shortens RKAB nickel production quotas from three-year to one-year allocations</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>In October 2025 Indonesia revised its RKAB mined-nickel production quota framework, introduced in 2023 as three-year allocations, shortening quotas to one year and requiring companies to reapply for quotas covering 2026 and 2027. IEA notes Indonesian policy developments increasingly shape global market dynamics: Indonesia accounts for almost two-thirds of mined and just under half of refined nickel supply.</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Outlook for nickel - p. 148</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Month precision (October 2025).</t>
+        </is>
+      </c>
+      <c r="W228" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>event_id=21479; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>21479</t>
+        </is>
+      </c>
+      <c r="Z228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>gcmo2026-nickel-indonesia-output-curb-and-revocations</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>production_curtailment</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Indonesia revokes non-compliant nickel quotas (Sept 2025); minister announces 2026 output curbs</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>In September 2025 Indonesia revoked [quotas/permits - source text ambiguous] due to non-compliance with rehabilitation or production requirements. Shortly after the October RKAB revision, the Minister of Energy and Natural Resources announced plans to curb nickel output in 2026 to support prices and government revenues. IEA: together these developments tightened expectations of future supply and contributed to a 20% nickel price increase between December 2025 and mid-2026.</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Outlook for nickel - pp. 148-149</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Dated to the September revocations (month precision). NOTE: the PDF text is garbled on exactly what was revoked ('the revocation of in September 2025') - verify against the report page before confirming. 2026-08-18 VERIFIED against rendered PDF p.149: the omission is IN THE PUBLISHED REPORT itself ('the revocation of  in September 2025') - an IEA editing error, not an extraction artifact. The revoked object is unnamed; context (RKAB framework discussion) suggests quotas/permits of non-compliant producers, but IEA's text is defective - treat the specifics as unconfirmed.</t>
+        </is>
+      </c>
+      <c r="W229" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>event_id=21480; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>21480</t>
+        </is>
+      </c>
+      <c r="Z229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>gcmo2026-nickel-indonesia-hpm-revision</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>price_floor_revision</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Indonesia revises HPM nickel ore benchmark, raising limonite floor price</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>In April 2026 Indonesia revised the mineral ore benchmark price (HPM), its official floor price for nickel ore. Limonite and saprolite floor prices were brought closer into alignment, raising the limonite floor relative to its nickel content. This supports domestic miners and royalty revenues while limiting the ability of (mostly Chinese-owned) smelters to push domestic ore prices down - but increases feedstock costs for HPAL operations producing battery-grade intermediates. Reportedly introduced with upward pressure on nickel prices.</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>geopolitical; financial_pressure</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Outlook for nickel - p. 149</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Month precision (April 2026).</t>
+        </is>
+      </c>
+      <c r="W230" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>event_id=21481; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>21481</t>
+        </is>
+      </c>
+      <c r="Z230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>gcmo2026-nickel-hpal-sulphur-cost-squeeze</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>input_cost_pressure</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Sulphur cost surge squeezes Indonesian HPAL output, tightening battery-grade nickel intermediates</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>An approximately 80% increase in sulphur prices, driven by a tighter global sulphur market, raises operating costs for HPAL facilities by roughly USD 1.7/kg of nickel (HPAL requires ~9 t sulphur per tonne of contained nickel). Combined with higher ore benchmark prices, this has weakened HPAL project economics and caused some HPAL facilities to decrease output, tightening availability of battery-grade intermediates (MHP). Nickel matte's sulphur intensity is ~3x lower, so the NPI/ferronickel market remains well supplied.</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>operational; material_concentration; financial_pressure</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Nickel; Cobalt</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Outlook for nickel - pp. 150-151</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>H1-2026 precision. Directly relevant to the sulphate/battery-grade stage our nickel score binds on. 2026-08-18: Cobalt added to materials (cobalt chapter pp.157-158: MHP is a Ni-Co intermediate; acid tightness is slowing MHP output. DRC copper-cobalt SxEw is also acid-dependent but near-term impact contained via elevated inventories and regional acid sourcing incl. Zambia).</t>
+        </is>
+      </c>
+      <c r="W231" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>event_id=21482; mat=2; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>21482</t>
+        </is>
+      </c>
+      <c r="Z231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>gcmo2026-nickel-indophil-corridor</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>IndoPhil Nickel Corridor formalizes Philippine ore feedstock supply to Indonesian HPAL</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Indonesia-Philippines nickel co-operation was recently formalised through the IndoPhil Nickel Corridor, aiming to provide stable feedstock supply for Indonesia's expanding HPAL capacity. As Indonesian policy restricts access to domestic ore, smelters imported almost 300 kt of nickel metal equivalent from the Philippines in 2025, up almost 50% from 2024. The Philippines is the world's second-largest holder of nickel reserves, largely limonite suited to HPAL processing. Detail from Latest policy developments (p.92): the corridor was formalised under an MOU in May 2026, committing to move 200,000 tonnes of ore per month from Philippine mines to Indonesian smelters starting June 2026.</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Outlook for nickel - p. 149</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>MOU May 2026 (per p.92); flows from June 2026. Supportive direction - display_only candidate (POSITIVE_POLICY subtype blocks scoring promotion).</t>
+        </is>
+      </c>
+      <c r="W232" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>event_id=21483; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>21483</t>
+        </is>
+      </c>
+      <c r="Z232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>mcs2026-aluminum-us-capacity-additions</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>US aluminum capacity additions 2025: Mt Holly restart plan, recycled mill ramps, expansions</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>US aluminum capacity moved upward through 2025: commissioning continued at a 650,000 t/y recycled flat-rolled mill in Mississippi (first coils June); an expanded Minnesota recycling plant began production in July (+55,000 t/y billet, total 165,000 t/y); plans were announced in August to restart &gt;50,000 t/y of idled capacity at a 229,000 t/y primary smelter in South Carolina (full production planned mid-2026); and a September expansion doubled capacity at a high-purity aluminum facility in Iowa. Two aluminum sheet facilities in Virginia and West Virginia closed in May and June.</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>material_concentration; operational</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Aluminum chapter - Events, Trends, and Issues (pp. 40-41)</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Year-aggregate positive row - display_only candidate. Includes the two sheet-facility closures for balance.</t>
+        </is>
+      </c>
+      <c r="W233" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>event_id=21484; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>21484</t>
+        </is>
+      </c>
+      <c r="Z233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>mcs2026-aluminum-sanciprian-restart</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>San Ciprian primary aluminum smelter (Spain, 228 kt/y) restarts after 2022 stoppage</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>In San Ciprian, Spain, a 228,000 t/y primary aluminum smelter restarted in 2025 after stopping production in 2022, with full production expected by mid-2026. USGS also notes an expected yearend start at a 500,000 t/y primary smelter in North Kalimantan, Indonesia, and resumed/upgraded Chinese smelter capacity across five provinces.</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>material_concentration</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Aluminum chapter - Events, Trends, and Issues (pp. 40-41)</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Year precision. Positive - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W234" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>event_id=21485; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>21485</t>
+        </is>
+      </c>
+      <c r="Z234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>mcs2026-copper-us-startups-2025</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>US copper supply startups 2025: new Arizona mine, Georgia secondary smelter, Kentucky refinery</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>As of September 2025, copper production had started during the year at a new mine in Arizona, a new secondary smelter in Georgia, and a new secondary refinery in Kentucky; one additional Arizona mine was expected to begin commercial operations by yearend. These startups partially offset the year's concentrator shutdowns and smelter-maintenance losses.</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>operational; material_concentration</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Copper chapter - Events, Trends, and Issues (pp. 72-73)</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Month precision (as-of September). Positive - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W235" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>event_id=21486; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>21486</t>
+        </is>
+      </c>
+      <c r="Z235" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>mcs2026-phosphate-blm-caribou-approval</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>BLM approves new phosphate rock mine in Caribou County, Idaho (replacement capacity)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>In October 2025 the US Bureau of Land Management approved a new phosphate rock mine in Caribou County, Idaho. The new mine will replace an existing mine when that mine is depleted within the next decade. US phosphate rock production has held near 20 million t/y as Florida producers contend with decreasing reserves and lower P2O5 content, driving rising imports.</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>regulatory_compliance; material_concentration</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Phosphate</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Phosphate Rock chapter - Events, Trends, and Issues (pp. 142-143)</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Government approval of replacement (not net-new) capacity - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W236" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>event_id=21487; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>21487</t>
+        </is>
+      </c>
+      <c r="Z236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>mcs2026-graphite-tanzania-doubling</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Tanzania more than doubles natural graphite production to 75,000 t</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>In 2025 Tanzania more than doubled graphite production to 75,000 tons, across operations in Manyara (Tanzanian and Chinese companies), Tanga, and Lindi (Australian company). Elsewhere, Brazil's Boa Sorte and Santa Cruz mines ramped up and a Russian company began production at Soyuznoye. USGS separately notes China still produced an estimated 82% of world natural graphite.</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>material_concentration</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>TZ</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Natural Graphite</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>Graphite (Natural) chapter - Events, Trends, and Issues (pp. 92-93)</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Year precision. Diversification-positive - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W237" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>event_id=21488; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>21488</t>
+        </is>
+      </c>
+      <c r="Z237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>mcs2026-ironore-minnesota-restart-project</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Construction restart announced at 7 Mt/y Minnesota iron ore mine and pelletizing plant</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>In December 2024 a company announced that construction would restart at a 7-million-t/y-capacity iron ore mine and pelletizing plant project in Minnesota, with startup expected in early 2026. Separately, in September-October 2025 two companies announced plans to explore rare-earth-element extraction at iron ore deposits in Nevada and the Minnesota/Michigan ranges.</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Iron Ore</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/periodicals/mcs2026/mcs2026.pdf</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>Iron Ore chapter - Events, Trends, and Issues (pp. 108-109)</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Month precision (Dec 2024 announcement). Positive - display_only candidate. USGS does not name the companies.</t>
+        </is>
+      </c>
+      <c r="W238" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>event_id=21489; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>21489</t>
+        </is>
+      </c>
+      <c r="Z238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>gcmo2026-cobalt-drc-2026-quota-allocations</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>quota_allocation</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>DRC 2026 cobalt quota allocations: CMOC 31,200 t, Glencore 22,800 t; KCC/Mutanda export standstill Q4 2025</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>The ARECOMS quota system approved in September 2025 took effect in October 2025: quotas distributed pro rata on historical export volumes, with exceptions for state entities (Entreprise Generale du Cobalt, STL) and exclusions for companies exporting &lt;100 t in 2024, refiners without mining, or depleted reserves; a strategic quota is reserved for ARECOMS with rights to buy back excess stocks. No allocation framework is published beyond 2027. The bite in the data: Glencore's KCC and Mutanda exported no cobalt in Q4 2025; CMOC's 2025 production rose 0.3% while sales fell 92% y/y. For 2026, CMOC received 31,200 t and Glencore 22,800 t of the 96,000 t total - levels IEA judges insufficient for projected intermediate supply requirements. Hydroxide inventories are building in-country (warehouse stockpiling, tailings storage, curtailments); cobalt metal prices approached USD 58,000/t in Q1 2026, more than 3x the prior year, and IEA projects the market shifts to deficit from 2026.</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>CMOC Group; Glencore</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>Outlook for cobalt - pp. 156-160</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Year-end anchor date (allocation publication date not stated in source). Extends the existing DRC quota rows with the 2026 allocation numbers - expect duplicate hints against the Feb-ban/Oct-quota rows; confirm as a distinct follow-on event or merge at triage.</t>
+        </is>
+      </c>
+      <c r="W239" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>event_id=21490; mat=1; co_link=SKIPPED[flag_off, 2 resolved]; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>21490</t>
+        </is>
+      </c>
+      <c r="Z239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>gcmo2026-cobalt-drc-strategic-reserve</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>strategic_reserve</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>DRC establishes ARECOMS-administered strategic critical minerals reserve</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>In April 2026 the DRC established a strategic reserve of critical minerals, administered by ARECOMS. The mechanism enables the state to withhold or release volumes in response to prevailing price conditions, meaning downstream buyers must factor in discretionary state interventions - increasing medium-term price uncertainty on top of the export quota regime.</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>Outlook for cobalt - p. 157</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Month precision (April 2026).</t>
+        </is>
+      </c>
+      <c r="W240" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>event_id=21491; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>21491</t>
+        </is>
+      </c>
+      <c r="Z240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>gcmo2026-cobalt-us-drc-partnership-deals</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>US-DRC Strategic Partnership yields ownership-diversification deals: Orion-Glencore MoU, Virtus-Chemaf</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Under the US-DRC Strategic Partnership Agreement: in January 2026 the DRC offered US investors access to state-owned mineral assets not committed under existing arrangements (Gecamines' Mutoshi copper-cobalt project, Sakima's coltan/gold, Cominiere's lithium licences); in February 2026 Glencore announced a non-binding MoU with the Orion Critical Minerals Consortium (backed by the US International Development Finance Corporation) for a potential 40% stake in Glencore's DRC assets; in April 2026 Virtus Minerals announced the acquisition of Chemaf (potential capacity of at least 20 kt/y cobalt hydroxide) and an MoU to supply US Strategic Metals' hydrometallurgical plant. IEA assesses these may attract non-Chinese capital but are unlikely to add significant volumes near-term.</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Glencore</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>Outlook for cobalt - pp. 157-158</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Dated to the latest component (April 2026); January and February components in summary. Supportive/ownership-diversification - display_only candidate (POSITIVE_POLICY blocks scoring promotion).</t>
+        </is>
+      </c>
+      <c r="W241" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>event_id=21492; mat=1; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>21492</t>
+        </is>
+      </c>
+      <c r="Z241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>gcmo2026-cobalt-indonesia-hpm-cobalt-pricing</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>price_floor_revision</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Indonesia's HPM revision prices cobalt content in nickel ore for the first time, adds 2% royalty</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>The April 2026 revision of Indonesia's mineral ore benchmark price (HPM) formula explicitly values cobalt content as a priced component of nickel ore for the first time, rather than treating it as a free-of-charge by-product, and subjects associated cobalt to a 2% royalty. Offtake contracts for MHP and other HPM-referenced intermediates must now account for cobalt's contribution to the benchmark price, further increasing processing costs for cobalt-bearing battery-grade intermediates. Indonesia is the second-largest and fastest-growing cobalt producer (~15% of 2025 mined supply, from 1.5% in 2020).</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>geopolitical; financial_pressure</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Cobalt; Nickel</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>Outlook for cobalt - p. 158</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Month precision (April 2026). Companion to gcmo2026-nickel-indonesia-hpm-revision (same measure, cobalt-specific provisions) - link or merge at triage as you prefer.</t>
+        </is>
+      </c>
+      <c r="W242" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>event_id=21493; mat=2; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>21493</t>
+        </is>
+      </c>
+      <c r="Z242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>gcmo2026-graphite-china-battery-anode-controls-oct-nov</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>export_licensing</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>China announces export controls on batteries, graphite anode materials and anode equipment (Oct 2025); suspends them for one year in November</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>On 9 October 2025 China announced major export controls on lithium-ion battery supply chains - expanding earlier targeted controls on graphite and high-performance LFP cathode material to cover LFP cathode materials, LFP batteries, graphite anode materials, cathode material precursors, and battery production equipment and technologies - simultaneously targeting the chokepoints where China holds the highest supply concentration (99% of LFP cell manufacturing). In November 2025 the measures were suspended for one year (to November 2026), alongside the rare earth controls. IEA: if fully enacted these would have severely restricted the rest of the world's ability to produce batteries near-term; risks remain elevated and the suspension can be lifted.</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Natural Graphite; Synthetic Graphite</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>Outlook for graphite - p. 167</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Announce-then-suspend captured in one row (same severity-trap discipline as the REE Oct/Nov row). Month precision. 2026-08-18 UPGRADED from geopolitical chapter pp.42-43: full 9-Oct scope (LFP cathode materials/batteries/precursors/equipment/technologies) - broader than the graphite-anode framing from p.167.</t>
+        </is>
+      </c>
+      <c r="W243" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>event_id=21494; mat=2; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>21494</t>
+        </is>
+      </c>
+      <c r="Z243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>gcmo2026-graphite-china-us-spherical-halt</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>export_licensing</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>China spherical graphite exports to the United States halted since April 2025 under targeted licensing</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Trade in battery-grade graphite from China has been affected by the export controls announced in 2024: total Chinese exports of spherical graphite decreased by 16% in 2025, and export licence issuance has in some cases been targeted to specific countries - with exports of spherical graphite to the United States halted since April 2025.</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Natural Graphite</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>Outlook for graphite - p. 167</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Month precision (halt effective April 2025). A destination-targeted halt - exactly the destination-specific exposure the structural score cannot see (documented limitation); the event feed is where it lives.</t>
+        </is>
+      </c>
+      <c r="W244" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>event_id=21495; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>21495</t>
+        </is>
+      </c>
+      <c r="Z244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>gcmo2026-graphite-mozambique-export-restrictions</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>beneficiation_requirement</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Mozambique restricts unprocessed material exports, mandates local value addition</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>In June 2026 Mozambique introduced restrictions on the export of unprocessed materials, mandated local value addition, and required 10% of mining revenues to be directed to local communities. Directly relevant to graphite: Mozambique (Balama) is the leading non-China flake graphite source.</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Syrah Resources</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Natural Graphite</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>Outlook for graphite - p. 167</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Month precision. Measure covers unprocessed materials generally; tagged to graphite as the battery-relevant exposure. Syrah linked as the principal affected operator (IEA does not name companies).</t>
+        </is>
+      </c>
+      <c r="W245" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>event_id=21496; mat=1; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>21496</t>
+        </is>
+      </c>
+      <c r="Z245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>gcmo2026-graphite-us-tariff-collapse</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>TARIFF</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>tariff_reduction</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>US tariffs on Chinese graphite fall from &gt;200% to ~35% after Supreme Court and USITC rulings</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>In the United States, total tariffs on graphite imported from China fell sharply from over 200% in February 2026 to about 35% by late March 2026, following rulings by the Supreme Court and the US International Trade Commission. This materially reduces the protection underpinning the 2025 AD/CVD determinations on Chinese graphite active anode material and reshapes incentives for ex-China anode investment.</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>geopolitical</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Natural Graphite; Synthetic Graphite</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>Outlook for graphite - pp. 167-168</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Month precision (late March 2026). SUPERSEDES much of mcs2026-graphite-us-adcvd-china-aam - adjudicate the pair together. Recommend display_only: a tariff REDUCTION cannot be represented by the impact math (severity is unsigned), so confirming it into scoring would read as added risk.</t>
+        </is>
+      </c>
+      <c r="W246" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>event_id=21497; mat=2; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>21497</t>
+        </is>
+      </c>
+      <c r="Z246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>gcmo2026-graphite-lindi-jumbo-administration</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>insolvency</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Lindi Jumbo graphite project (Tanzania) enters administration; operations constrained</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Some output entered the market from Tanzania's Lindi Jumbo project in 2025, although operations remained constrained after the project entered administration. Together with the Balama restart, Tanzanian and Mozambican supply reduced the top supplier's (China's) share of mined graphite output to around 80% in 2025, from 84% in 2023.</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>TZ</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Natural Graphite</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>Outlook for graphite - p. 166</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Year precision. Counterweight to mcs2026-graphite-tanzania-doubling - link at triage.</t>
+        </is>
+      </c>
+      <c r="W247" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>event_id=21498; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>21498</t>
+        </is>
+      </c>
+      <c r="Z247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>gcmo2026-graphite-exchina-project-scalebacks</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>project_scaleback</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>SGL (Poland) and Tokai COBEX (France) scale back graphite capacity plans under Chinese price pressure</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Projects outside China revised or scaled back planned capacity expansions in response to weaker project economics: recent examples include SGL's graphite facilities in Poland and Tokai COBEX's project in France, both adjusting ambitions amid sustained price pressure, high operating costs and strong competition from the dominant supplier. Concentration-negative for the ex-China anode buildout.</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>material_concentration</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Synthetic Graphite; Natural Graphite</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>Outlook for graphite - p. 166</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Year precision. Risk-direction capacity change (no POSITIVE subtype - eligible for scoring at triage discretion).</t>
+        </is>
+      </c>
+      <c r="W248" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>event_id=21499; mat=2; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>21499</t>
+        </is>
+      </c>
+      <c r="Z248" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>gcmo2026-graphite-needle-coke-hormuz</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>input_cost_pressure</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Hormuz shipping disruptions push needle coke prices up &gt;20%, pressuring synthetic anode costs</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Needle coke prices rose in 2025 (calcined petroleum needle coke +4% y/y) on persistent supply deficits in China. In early 2026, shipping disruptions in the Strait of Hormuz pushed up oil prices with knock-on effects on needle coke markets: prices rose more than 20% since the start of the conflict, with uncalcined needle coke reaching USD 928/t in April 2026. IEA notes these increases could materially affect the cost base of synthetic graphite anode production - though the industry is shifting to a multi-feedstock model (low-sulphur petroleum coke) that reduces needle-coke exposure.</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>operational; financial_pressure</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Synthetic Graphite</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>Outlook for graphite - pp. 166-167</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>April 2026 price point; conflict start date not stated in source.</t>
+        </is>
+      </c>
+      <c r="W249" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>event_id=21500; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>21500</t>
+        </is>
+      </c>
+      <c r="Z249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>gcmo2026-graphite-nmg-matawinie-fid</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Nouveau Monde Graphite confirms FID for Matawinie mine (~100 kt/y before 2030)</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>In Canada, Nouveau Monde Graphite confirmed the final investment decision for its Matawinie Mine project, expected to produce around 100 kt/y of graphite starting before 2030. Part of the mined-supply diversification IEA projects will cut China's share of mined graphite from 80% (2025) to 53% (2035) - while China's battery-grade share falls only from 94% to 91%.</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>material_concentration</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Natural Graphite</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>Outlook for graphite - p. 172</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>FID date not stated in source - year-end anchor. Positive - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W250" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>event_id=21501; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>21501</t>
+        </is>
+      </c>
+      <c r="Z250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>gcmo2026-ree-mp-dow-apple-partnership</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>MP Materials lands US Department of War partnership with USD 110/kg NdPr floor price, plus USD 500M Apple deal</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>In July 2025 MP Materials, operator of one of the only integrated rare earth facilities outside China, announced a landmark partnership with the US Department of War to expand domestic permanent magnet production - including support for its Independence magnet facility and development of the large-scale 10X manufacturing campus, with a committed floor price of USD 110/kg for neodymium-praseodymium products. MP also signed a USD 500 million agreement with Apple to purchase magnets produced at Independence using recycled feedstock, and the companies agreed to establish a recycling line at Mountain Pass for end-of-life products and scrap.</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>material_concentration; geopolitical</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>MP Materials</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements; Neodymium; Praseodymium</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>Outlook for rare earth elements - pp. 177-178</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Month precision (July 2025). Supportive - display_only candidate. The $110/kg floor is the reference price later matched by the Lynas deals.</t>
+        </is>
+      </c>
+      <c r="W251" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>event_id=21502; mat=3; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>21502</t>
+        </is>
+      </c>
+      <c r="Z251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>gcmo2026-ree-lynas-supply-agreements</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Lynas signs DoW and Japan supply deals at USD 110/kg NdPr floor; half of future heavy REO to Japan</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Lynas Rare Earths signed a binding letter of intent with the US Department of War for a four-year light and heavy rare earth oxide supply agreement (~USD 96 million allocated for purchases, with a USD 110/kg NdPr oxide floor price), and a 12-year supply arrangement with Japan at the same floor price - which also allocates to Japan around half of Lynas's future heavy rare earth oxide production via the Japan Australia Rare Earths partnership (Sojitz / JOGMEC). In October 2025 Lynas partnered with US magnet manufacturer Noveon Magnetics (light + heavy materials), and in March 2026 signed a co-operation deal with Korea's LS Eco Energy including plans for a metal processing facility in Viet Nam.</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>material_concentration; geopolitical</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Lynas</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>Outlook for rare earth elements - pp. 178-179</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Dated to the latest component (March 2026); earlier components in summary. Supportive - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W252" s="20" t="inlineStr">
+        <is>
+          <t>loaded_partial</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>event_id=21503; mat=1; co_link=0; fac=0; reg=0; geo=2; warnings=[unresolved_companies=1[Lynas]]</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>21503</t>
+        </is>
+      </c>
+      <c r="Z252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>gcmo2026-ree-usa-rare-earth-consolidation</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>POSITIVE_DEVELOPMENT</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>USA Rare Earth assembles mine-to-magnet chain: LCM, Serra Verde, Carester stake, ~USD 3.6B backing</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Within roughly a year USA Rare Earth signed multiple agreements toward a mine-to-magnet value chain: acquisition of UK-based metallisation company Less Common Metals (USD 125 million equity investment), acquisition of Brazil's Serra Verde rare earth mining company, a planned all-stock purchase of Texas Mineral Resources Corporation, and a 12.5% equity stake in the French metal and alloy facility operated by Carester. The buildout is supported by an estimated USD 1.6 billion in US government financing and equity support plus ~USD 2 billion raised privately. Separately, the DOE NETL signed a letter of intent with USA Rare Earth on digital-twin technology for heavy rare earth separation (Wheat Ridge laboratory / Round Top deposit).</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>material_concentration</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>Outlook for rare earth elements - pp. 176-178</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Year anchor (deal dates span &lt;12 months; individual dates not all stated). Supportive - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W253" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>event_id=21504; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>21504</t>
+        </is>
+      </c>
+      <c r="Z253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>gcmo2026-ree-india-magnet-scheme</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>India approves ~EUR 780M integrated permanent-magnet manufacturing scheme</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>In November 2025 the Indian government approved an INR 72.8 billion (~EUR 780 million) scheme to develop integrated permanent magnet manufacturing capacity covering the full value chain from rare earth oxides to finished magnets. Complementary measures: the 2026 Union Budget introduced dedicated rare earth industrial corridors in Andhra Pradesh, Kerala and Odisha; a recycling incentive scheme sets aside INR 1,500 crore (~EUR 145 million); and the Geological Survey of India has launched 563 critical-mineral exploration projects since 2021 (including rare earths).</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>material_concentration</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>Outlook for rare earth elements - pp. 176-177</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Month precision on the scheme approval. Supportive - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W254" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>event_id=21505; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>21505</t>
+        </is>
+      </c>
+      <c r="Z254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>gcmo2026-ree-g7-diversification-target</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>G7 leaders commit to cutting single-supplier rare earth and magnet dependency below 60% by 2030</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>In June 2026, G7 member countries agreed to reduce dependencies on rare earths and permanent magnets from a single supplier to under 60% by 2030, in the G7 leaders' declaration on securing critical mineral supply chains. IEA frames this within an emerging approach of direct government support to supply chains - financing, floor prices, strategic reserves, bilateral frameworks (US-Australia, US-Saudi Arabia, Brazil-India, France-Japan/Caremag) - rather than enabling policy alone.</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>CA; GB; DE; FR; IT; JP</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>Outlook for rare earth elements - p. 177</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Month precision. Multilateral declaration - primary_country US is a convention (no G7 code); secondaries carry the rest. Supportive - display_only candidate. 2026-08-18: context from pp.93: target is a single NON-G7 supplier; precursors = Canada's 2025 G7 presidency Critical Minerals Action Plan + Standards-Based Markets Roadmap (procurement, financial incentives, trade measures, PRICE FLOORS as instruments); IEA Critical Minerals Security Programme reinforced Feb 2026.</t>
+        </is>
+      </c>
+      <c r="W255" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>event_id=21506; mat=1; co_link=0; fac=0; reg=0; geo=7</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>21506</t>
+        </is>
+      </c>
+      <c r="Z255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>gcmo2026-copper-grasberg-mudflow</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>INCIDENT</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>mudflow</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Grasberg mudflow disaster halves 2025 output at world's second-largest copper mine</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>A disastrous mudflow at Grasberg (Indonesia) in September 2025 caused major disruption and fatalities. Grasberg is the world's second-largest copper mine, accounting for almost 4% of global mined production in 2024; 2025 production was around half of 2024 levels, significant disruptions are expected throughout 2026, and full recovery is only anticipated in 2028. Together with Kamoa-Kakula, 2025 disruptions totalled 1.5 Mt (~6% of global mined supply), tipping the refined market into deficit and driving copper past USD 12,000/t in December 2025.</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>operational; material_concentration</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Freeport-McMoRan</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>Outlook for copper - pp. 125-126</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Month precision. IEA does not name the operator (Freeport-McMoRan) - may already be in corpus via the Freeport walkthrough; check at triage.</t>
+        </is>
+      </c>
+      <c r="W256" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>event_id=21507; mat=1; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>21507</t>
+        </is>
+      </c>
+      <c r="Z256" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>gcmo2026-copper-kamoa-kakula-flooding</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>INCIDENT</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>flooding</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Seismic flooding cuts Kamoa-Kakula production almost one-third below guidance</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Seismic activity at Kamoa-Kakula (DRC), the country's largest and the world's fourth-largest copper mine by 2024 production, caused severe flooding and infrastructure damage, cutting 2025 production almost one-third relative to guidance. Rehabilitation requirements mean 2026 guidance is expected to remain below 2024 levels. One of the two major disruptions (with Grasberg) totalling 1.5 Mt in 2025.</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>operational; material_concentration</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>Outlook for copper - p. 126</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Year precision (source does not date the seismic event). IEA does not name the operator (Ivanhoe Mines / Zijin JV).</t>
+        </is>
+      </c>
+      <c r="W257" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>event_id=21508; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>21508</t>
+        </is>
+      </c>
+      <c r="Z257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>gcmo2026-hormuz-closure-sulphur-shock</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>logistics_chokepoint</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Strait of Hormuz closure triggers global sulphur/sulphuric acid supply shock</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>The Middle East conflict and effective closure of the Strait of Hormuz in February 2026 caused a supply shock for sulphur and sulphuric acid: around half of global seaborne sulphur trade passes through the Strait, and Gulf countries plus Iran account for a quarter of global sulphur supply. Over 15% of global primary copper is produced via acid-dependent SxEw - the DRC (almost 1.5 Mt; ~45% of its copper output, acid at ~20% of costs) and Chile (1.2 Mt) are most vulnerable, with Mexico, the US and Zambia also exposed. Some producers' sulphur/acid inventories are reportedly down to 30-60 days, with growing warnings of production cuts. Iran's own ~400 kt of copper cannot access the global market due to the closure.</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>operational; geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>IR</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>CD; CL; ZM; MX; US; ID</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Copper; Cobalt; Nickel; Phosphate; Manganese; Lithium; Rare Earth Elements</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>Outlook for copper - pp. 126-127</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Month precision (closure February 2026). Upstream cause of the HPAL sulphur squeeze (gcmo2026-nickel-hpal-sulphur-cost-squeeze) and the needle-coke price spike (gcmo2026-graphite-needle-coke-hormuz) - link at triage. 2026-08-18: Phosphate + Manganese added (GCMO pp.189-190): phosphate exports from Jordan disrupted by the closure; sulphuric acid is a key PPA input (PPA &gt;USD 1,500/t Q1 2026, +4%); manganese sulphate contracts settled above USD 1,000/t on acid and ore costs. 2026-08-18 EXTENDED (pp.44-57): conflict start 28 Feb 2026; sulphuric acid doubled USD 144/t (Feb) to 283/t (Apr 2026); ~60% of battery-grade Li chemicals use acid processing - acid rose from 3% to &gt;11% of hard-rock Li chemical cash costs by end-May 2026 (now the largest component); REE acid bake-and-leach C1 costs 5% -&gt; &gt;20%; Ni/Co/Mn sulphate prices all up; PPA +30% Q1 2026. Prior tightness: Russia sulphur export ban + refinery damage 2025. Consider splitting per-material at triage if one row is too broad.</t>
+        </is>
+      </c>
+      <c r="W258" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>event_id=21509; mat=7; co_link=0; fac=0; reg=0; geo=7</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>21509</t>
+        </is>
+      </c>
+      <c r="Z258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>gcmo2026-china-sulphuric-acid-export-ban</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>export_ban</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>China bans sulphuric acid exports through end-2026, hitting a quarter of ex-China acid needs</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>China implemented a ban on sulphuric acid exports from May 2026 until the end of the year, affecting almost a quarter of ex-China acid needs - compounding the Hormuz-driven sulphur shock for acid-dependent copper SxEw and HPAL nickel-cobalt processing. The ban is bifurcating acid prices: rising outside China (supporting ex-China smelter by-product economics) while falling inside China on surplus domestic supply. Sequence detail (pp.51-52): China first announced an export CAP for January-April 2026 to safeguard domestic supply (~50% y/y export decline), then the full halt from May 2026 to yearend. The restrictions cover both sulphur-burner and smelter by-product acid, with an exemption only for electronic-grade (semiconductor) acid. China exported 4.7 Mt of sulphuric acid in 2025, with Chile and Indonesia importing half of the total.</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>geopolitical; operational</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Copper; Cobalt; Nickel</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>Outlook for copper - pp. 126-127, 131</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Month precision. Pair with the Hormuz row at triage - distinct measures, same input chain.</t>
+        </is>
+      </c>
+      <c r="W259" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>event_id=21510; mat=3; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>21510</t>
+        </is>
+      </c>
+      <c r="Z259" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>gcmo2026-copper-us-semis-tariffs-inventory</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TARIFF</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>section_232</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>US tariffs on semi-finished copper products distort global inventories; cathode tariff looms</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>The United States implemented tariffs on semi-finished copper products and copper-intensive derivatives in 2025. Refined copper (cathode) was excluded but remained under consideration - the prospect drove net imports of 1.5 Mt of cathode into the US, a 0.5 Mt COMEX inventory build, low inventories at Asian and European exchanges, and significant LME/CME arbitrage. Renewed tariff concern has recently increased again.</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>geopolitical</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>Outlook for copper - p. 128</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Year precision. Cross-reference: the MCS copper row attributes the 2025 COMEX price surge primarily to this tariff uncertainty.</t>
+        </is>
+      </c>
+      <c r="W260" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>event_id=21511; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>21511</t>
+        </is>
+      </c>
+      <c r="Z260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>gcmo2026-copper-tcrc-zero-midstream-squeeze</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>margin_collapse</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Copper smelter TC/RC benchmark settles at USD 0/t; ex-China smelters cut output on record-low fees</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>The annual copper treatment/refining charge benchmark (Antofagasta-Chinese smelters) settled at USD 0/tonne in January 2026 - the lowest ever - with spot TC/RCs negative since 2024. Ex-China smelter utilisation fell below 70% (vs 85% in China); some custom smelters outside China cut production or received emergency government support to avoid closure. China's top smelters agreed to cut capacity by over 10% in 2026 and the government halted ~2 Mt of planned new smelting capacity. IEA warns the dynamic could repeat the nickel pattern: uneconomic ex-China production consolidating midstream concentration in China (already &gt;50% of global smelting).</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>financial_pressure; material_concentration</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>Outlook for copper - pp. 129-133</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>January 2026 benchmark settlement; broader squeeze is 2024-2026. Midstream-concentration risk event rather than a single facility disruption.</t>
+        </is>
+      </c>
+      <c r="W261" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>event_id=21512; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>21512</t>
+        </is>
+      </c>
+      <c r="Z261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>gcmo2026-copper-tiamaria-permit-whiplash</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>REGULATORY_COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>permitting_restriction</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Peru revokes then reauthorises Tia Maria permit within 11 days</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>In April [2026] the permit for Southern Copper's long-delayed Tia Maria SxEw project in Peru was revoked before being reauthorised 11 days later - cited by IEA as demonstrating the uncertainty and challenges of bringing major new copper projects online. Peru's 2035 supply outlook nonetheless improved ~300 kt on Antamina life extension and Tia Maria.</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>regulatory_compliance</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Southern Copper</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>Outlook for copper - p. 136</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Month stated (April), year inferred from report context (2026) - flag if the PDF page shows otherwise.</t>
+        </is>
+      </c>
+      <c r="W262" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>event_id=21513; mat=1; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>21513</t>
+        </is>
+      </c>
+      <c r="Z262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>gcmo2026-manganese-gemco-cyclone-repause</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>OPERATIONAL_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>weather_event</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>New cyclone pauses GEMCO manganese operations again in March 2026</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Operations at South32's GEMCO mine on Groote Eylandt (Australia) - the world's second-largest manganese mine - were paused again in March 2026 due to a new cyclone, after the major 2024 cyclone disruption that had driven large manganese ore and sulphate price increases. IEA cites the repeat event as highlighting weather risk to major manganese assets; the March 2026 disruption added renewed pressure to rising 2026 manganese prices (compounded by acid and diesel input costs from the Middle East conflict).</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>operational; material_concentration</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>South32</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Manganese</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>Other key materials - Manganese, pp. 188-189</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Month precision. Second weather disruption at the same asset within ~18 months - links to mcs2026-manganese-gemco-resumption.</t>
+        </is>
+      </c>
+      <c r="W263" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>event_id=21514; mat=1; co_link=SKIPPED[flag_off, 1 resolved]; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>21514</t>
+        </is>
+      </c>
+      <c r="Z263" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>gcmo2026-phosphate-egypt-export-halt</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>export_contract_halt</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Egypt halts new phosphate export contracts to force domestic value addition</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Egypt's Ministry of Petroleum and Mineral Resources announced it would not sign any new phosphate export contracts, as the government shifts from exporting raw materials to producing higher-value-added products such as phosphate fertilisers. The announcement contributed to rising phosphate rock prices, alongside the Jordan export disruption from the Hormuz closure - with knock-on pressure on purified phosphoric acid (PPA) prices and LFP cathode costs.</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Phosphate</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>Other key materials - Phosphoric acid, p. 190</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Announcement date not stated in source - H1-2026 anchor; verify before confirming. Resource-nationalism measure in the classic beneficiation-mandate family.</t>
+        </is>
+      </c>
+      <c r="W264" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>event_id=21515; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>21515</t>
+        </is>
+      </c>
+      <c r="Z264" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>gcmo2026-aluminum-middle-east-disruptions</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>INCIDENT</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>conflict_damage</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Middle East conflict knocks out one-third of the region's aluminium output; Alba and EGA hit</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>The Middle East conflict (started 28 February 2026) directly disrupted regional aluminium production - 8% of global primary supply, one-fifth excluding China, and &gt;10% of pre-conflict aluminium imports for the EU, Japan, Korea and Mexico (~20% for the US). Aluminium Bahrain (Alba), the world's largest smelter outside China (1.6 Mt), declared force majeure on Hormuz logistics, shut three lines (19% of capacity) and was operating at 30% in April 2026; Qatalum (0.65 Mt) declared force majeure on gas supply from Ras Laffan and ran at 60%. In late March, strikes damaged Alba and Emirates Global Aluminium's Al Taweelah plant - the latter halted on power-facility damage, a particular concern as a key high-purity aluminium producer for aerospace. One-third of Middle East output was lost; restarts take 6-12 months. Prices hit a four-year high near USD 3,700/t in April 2026; the Rotterdam premium rose 60% Feb-Apr; green petroleum coke (anode feedstock) rose ~35%.</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>operational; geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>BH</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>QA; AE; IR</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>Geopolitical developments - pp. 45-49</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Month precision (strikes late March; utilisation figures April 2026). Largest single aluminium supply event in the corpus - candidate for the aluminium page's live-signal context.</t>
+        </is>
+      </c>
+      <c r="W265" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>event_id=21516; mat=1; co_link=0; fac=0; reg=0; geo=4</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>21516</t>
+        </is>
+      </c>
+      <c r="Z265" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>gcmo2026-aluminum-china-rebate-removal-capacity-cap</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>export_rebate_removal</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>China removes aluminium semi-product export tax rebates; hits its 45 Mt production cap in 2025</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>China removed some export tax rebates on semi-finished aluminium products effective 1 December 2024, contributing to decreasing aluminium exports. Separately, China reached in 2025 the 45 Mt primary aluminium production cap set in 2017 - constraining supply growth as demand rose ~7% from 2023-2025. LME inventories fell from &gt;1 Mt (June 2024) to ~350 kt (June 2025); the US raised tariffs on most imported aluminium products to 50% in 2025.</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>Geopolitical developments - pp. 48-49</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Rebate removal precisely dated; cap-reached is a 2025 structural fact folded in. US 50% tariff overlaps mcs2026-aluminum-us-section232-tariffs - cross-check at triage.</t>
+        </is>
+      </c>
+      <c r="W266" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>event_id=21517; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>21517</t>
+        </is>
+      </c>
+      <c r="Z266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>gcmo2026-phosphate-china-fertiliser-export-halt</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>export_ban</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>China halts phosphate fertiliser exports from December 2025, expected through August 2026</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>China halted phosphate fertiliser exports in December 2025, citing global sulphuric acid price spikes, with the restriction expected to last until August 2026. The Philippines, Kenya and Myanmar are most vulnerable (31%, 14% and 13% of exposed imports from China in 2025). Combined with sulphur-chain disruption, IEA assesses the entire fertiliser production chain as at risk, with food-security implications for developing countries.</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Phosphate</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>Geopolitical developments - pp. 52-53</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Month precision. Fertiliser-side phosphate event - distinct from the PPA/battery-grade thread but the same underlying acid squeeze.</t>
+        </is>
+      </c>
+      <c r="W267" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>event_id=21518; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>21518</t>
+        </is>
+      </c>
+      <c r="Z267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>gcmo2026-aluminum-guinea-bauxite-export-control</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>proposed_export_control</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Guinea proposes new bauxite export control effective June 2026</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Per GCMO 2026's export-controls table: Guinea - 34% of global bauxite mining - proposed a new export control to be effective in June 2026. A binding Guinean control would be the largest single-country upstream measure in the aluminium chain.</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>GN</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>Geopolitical developments - export controls table, p. 39</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Effective date given; announcement date not stated. PROPOSED measure - verify enactment before any scoring use (suspended-measure discipline).</t>
+        </is>
+      </c>
+      <c r="W268" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>event_id=21519; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>21519</t>
+        </is>
+      </c>
+      <c r="Z268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>gcmo2026-manganese-gabon-export-ban-proposal</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>proposed_export_ban</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Gabon proposes ban on raw manganese exports starting 2029</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Per GCMO 2026's export-controls table: Gabon - about a quarter of global mined manganese supply in 2025, the world's second-largest supplier - proposed a ban on raw mineral exports to start in 2029, in the beneficiation-mandate family of measures.</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Manganese</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>Geopolitical developments - export controls table, p. 39; Other key materials p. 189</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Proposal announcement date not stated (2025/2026 window) - year anchor. Future-dated start (2029): keep display-only until enacted.</t>
+        </is>
+      </c>
+      <c r="W269" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>event_id=21520; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>21520</t>
+        </is>
+      </c>
+      <c r="Z269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>gcmo2026-nickel-philippines-fiscal-regime-export-ban-proposal</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>resource_nationalism</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Philippines enacts Enhanced Fiscal Regime for mining; proposes raw nickel ore export ban from 2030</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>The Philippines officially enacted the Enhanced Fiscal Regime for Large-Scale Metallic Mining in September 2025, introducing a royalty structure to increase government revenue from mineral extraction. Separately (export-controls table), the Philippines proposed a ban on raw mineral exports to start in 2030. Both matter disproportionately for nickel: the Philippines holds ~11% of mining share, is the world's second-largest nickel reserve holder, and exported ~300 kt NiEq of ore feedstock to Indonesian HPAL smelters in 2025 (the IndoPhil corridor commits 200 kt/month from June 2026).</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>Geopolitical developments p. 39; Latest policy developments pp. 92-93</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Fiscal regime month-dated; export-ban proposal undated with 2030 start - display-only until enacted. Direct tension with Indonesia's feedstock dependence - flag in the nickel narrative.</t>
+        </is>
+      </c>
+      <c r="W270" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>event_id=21521; mat=1; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>21521</t>
+        </is>
+      </c>
+      <c r="Z270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>gcmo2026-china-feb2025-licensing-wave</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>export_licensing</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>China's February 2025 export-licensing wave: bismuth, indium, molybdenum, tellurium, tungsten</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>In February 2025 China introduced export licensing on bismuth, indium, molybdenum, tellurium and tungsten. The number of Chinese tariff codes under export control tripled from December 2023 to April 2025; the export value of controlled items exceeded USD 11 billion in 2025. For most products trade continued with added friction and cost, but some flows significantly decreased or stopped - notably permanent magnets, antimony oxide, and tungsten carbide and powder. In January 2025 China also proposed an export control on lithium refining technology.</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Bismuth; Indium; Molybdenum; Tellurium; Tungsten</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>Geopolitical developments - pp. 39-41</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Non-launch corpus materials (all scored: Bi 94.89, Te 89.51, W 90.05...). Lithium refining-technology control kept as a note, not a material tag (technology measure, not a lithium trade flow).</t>
+        </is>
+      </c>
+      <c r="W271" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>event_id=21522; mat=5; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>21522</t>
+        </is>
+      </c>
+      <c r="Z271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>gcmo2026-china-us-ban-suspensions-ga-ge-sb</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>export_ban_suspension</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>China suspends its US-directed export bans on gallium, germanium and antimony until November 2026</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>China suspended its bans on exports of gallium, germanium and antimony to the United States until November 2026 (part of the November 2025 de-escalation that also suspended the October REE and battery controls). Exports of antimony oxide to Japan, Chinese Taipei and the United States had been halted since September 2024; those flows and dual-use items like tungsten carbide had been among the most fully disrupted by the control regime.</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>geopolitical</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Gallium; Germanium; Antimony</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>Geopolitical developments - pp. 39-41</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Suspension of restrictions - like the tariff-collapse row, the impact math cannot represent risk REDUCTIONS; display_only recommended. Ga/Ge/Sb are corpus-scored materials (Ga 100.0).</t>
+        </is>
+      </c>
+      <c r="W272" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>event_id=21523; mat=3; co_link=0; fac=0; reg=0; geo=2</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>21523</t>
+        </is>
+      </c>
+      <c r="Z272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>gcmo2026-ree-us-project-vault</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>US launches Project Vault: USD 12B demand-driven strategic critical minerals reserve</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>In February 2026 the United States announced Project Vault (the US Strategic Critical Minerals Reserve): an independently governed public-private partnership backed by up to USD 12 billion (~USD 10 billion Export-Import Bank financing + ~USD 2 billion private), stockpiling based on manufacturer commitments and supply-chain needs, with rare earth elements receiving early emphasis. Complementary instruments include equity stakes in mining companies, bilateral price-floor frameworks and offtake-linked financing. The US also launched the FORGE multilateral forum in February 2026 and had concluded &gt;20 critical-minerals frameworks/MOUs by early 2026.</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>Latest policy developments - pp. 92-94</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Month precision. Supportive - display_only candidate. REE tagged per stated early emphasis; reserve scope is multi-mineral.</t>
+        </is>
+      </c>
+      <c r="W273" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>event_id=21524; mat=1; co_link=0; fac=0; reg=0; geo=1</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>21524</t>
+        </is>
+      </c>
+      <c r="Z273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>gcmo2026-quad-critical-minerals-framework</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>TRADE_POLICY</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>POSITIVE_POLICY</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Quad announces Critical Minerals Initiative Framework mobilising up to USD 20B</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>In May 2026 Australia, India, Japan and the United States announced the Quad Critical Minerals Initiative Framework (advancing the July 2025 Quad initiative), coordinating investment, policy tools and supply chains across the full minerals value chain and aiming to mobilise up to USD 20 billion to reduce reliance on concentrated supply via joint mining, processing and recycling development.</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>geopolitical; material_concentration</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>AU; IN; JP</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Rare Earth Elements</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>https://www.iea.org/reports/global-critical-minerals-outlook-2026</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>Latest policy developments - p. 92</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>government_publication</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Month precision. Multi-mineral framework - REE tagged as the flagship exposure; broaden tags at triage if desired. Supportive - display_only candidate.</t>
+        </is>
+      </c>
+      <c r="W274" s="23" t="inlineStr">
+        <is>
+          <t>loaded</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>event_id=21525; mat=1; co_link=0; fac=0; reg=0; geo=4</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>21525</t>
+        </is>
+      </c>
+      <c r="Z274" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24869,7 +31259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -25035,25 +31425,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAPACITY_CHANGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Supply capacity start / restart / expansion / closure reversal (report extractions). Pair with POSITIVE_POLICY or POSITIVE_DEVELOPMENT subtype when supportive - the subtype blocks scoring promotion (2026-08-17).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>risk_categories (multi-select, comma-separated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>material_concentration</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Affects supply/demand concentration of a material</t>
         </is>
       </c>
     </row>
@@ -25061,12 +31450,12 @@
       <c r="A17" s="5" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>geopolitical</t>
+          <t>material_concentration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Geopolitical risk — sanctions, trade war, conflict</t>
+          <t>Affects supply/demand concentration of a material</t>
         </is>
       </c>
     </row>
@@ -25074,12 +31463,12 @@
       <c r="A18" s="5" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>geopolitical</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Production disruption, facility status</t>
+          <t>Geopolitical risk — sanctions, trade war, conflict</t>
         </is>
       </c>
     </row>
@@ -25087,12 +31476,12 @@
       <c r="A19" s="5" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>regulatory_compliance</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Compliance burden, license, permit</t>
+          <t>Production disruption, facility status</t>
         </is>
       </c>
     </row>
@@ -25100,35 +31489,35 @@
       <c r="A20" s="5" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>financial_pressure</t>
+          <t>regulatory_compliance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Litigation provisions, debt, capex commitments</t>
+          <t>Compliance burden, license, permit</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>financial_pressure</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Litigation provisions, debt, capex commitments</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>severity_score calibration (0.00-1.00, your judgment)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0.90-1.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Catastrophic — major facility shutdown, force majeure invoked, multi-year recovery</t>
         </is>
       </c>
     </row>
@@ -25136,12 +31525,12 @@
       <c r="A24" s="5" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.70-0.89</t>
+          <t>0.90-1.00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>High — significant disruption, multi-month impact, regulatory action</t>
+          <t>Catastrophic — major facility shutdown, force majeure invoked, multi-year recovery</t>
         </is>
       </c>
     </row>
@@ -25149,12 +31538,12 @@
       <c r="A25" s="5" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.50-0.69</t>
+          <t>0.70-0.89</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Moderate — single-quarter impact, contained incident, contingent liability triggered</t>
+          <t>High — significant disruption, multi-month impact, regulatory action</t>
         </is>
       </c>
     </row>
@@ -25162,12 +31551,12 @@
       <c r="A26" s="5" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.30-0.49</t>
+          <t>0.50-0.69</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Low — informational risk, minor incident, ongoing situation</t>
+          <t>Moderate — single-quarter impact, contained incident, contingent liability triggered</t>
         </is>
       </c>
     </row>
@@ -25175,12 +31564,12 @@
       <c r="A27" s="5" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.10-0.29</t>
+          <t>0.30-0.49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Very low — settlement progress, positive policy, structural improvement</t>
+          <t>Low — informational risk, minor incident, ongoing situation</t>
         </is>
       </c>
     </row>
@@ -25188,35 +31577,35 @@
       <c r="A28" s="5" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.00-0.09</t>
+          <t>0.10-0.29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Negligible — disclosure only, no material change</t>
+          <t>Very low — settlement progress, positive policy, structural improvement</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.00-0.09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Negligible — disclosure only, no material change</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>confidence_score guidance</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0.95-1.00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Quoted verbatim from audited annual report (10-K, 20-F)</t>
         </is>
       </c>
     </row>
@@ -25224,12 +31613,12 @@
       <c r="A32" s="5" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.85-0.94</t>
+          <t>0.95-1.00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Quoted from press release, interim filing (10-Q, 6-K)</t>
+          <t>Quoted verbatim from audited annual report (10-K, 20-F)</t>
         </is>
       </c>
     </row>
@@ -25237,12 +31626,12 @@
       <c r="A33" s="5" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.70-0.84</t>
+          <t>0.85-0.94</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>News article from reputable source (FT, Reuters, Bloomberg)</t>
+          <t>Quoted from press release, interim filing (10-Q, 6-K)</t>
         </is>
       </c>
     </row>
@@ -25250,12 +31639,12 @@
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0.50-0.69</t>
+          <t>0.70-0.84</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Trade press, analyst report</t>
+          <t>News article from reputable source (FT, Reuters, Bloomberg)</t>
         </is>
       </c>
     </row>
@@ -25263,35 +31652,35 @@
       <c r="A35" s="5" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>&lt;0.50</t>
+          <t>0.50-0.69</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Don't enter — too uncertain for manual capture</t>
+          <t>Trade press, analyst report</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>&lt;0.50</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Don't enter — too uncertain for manual capture</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>source_form_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>US annual report (domestic issuer)</t>
         </is>
       </c>
     </row>
@@ -25299,12 +31688,12 @@
       <c r="A39" s="5" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20-F</t>
+          <t>10-K</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US annual report (foreign issuer)</t>
+          <t>US annual report (domestic issuer)</t>
         </is>
       </c>
     </row>
@@ -25312,12 +31701,12 @@
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10-Q</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US quarterly report</t>
+          <t>US annual report (foreign issuer)</t>
         </is>
       </c>
     </row>
@@ -25325,12 +31714,12 @@
       <c r="A41" s="5" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>10-Q</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US current report (event-driven)</t>
+          <t>US quarterly report</t>
         </is>
       </c>
     </row>
@@ -25338,12 +31727,12 @@
       <c r="A42" s="5" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6-K</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foreign current report</t>
+          <t>US current report (event-driven)</t>
         </is>
       </c>
     </row>
@@ -25351,12 +31740,12 @@
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>40-F</t>
+          <t>6-K</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Canadian annual report</t>
+          <t>Foreign current report</t>
         </is>
       </c>
     </row>
@@ -25364,12 +31753,12 @@
       <c r="A44" s="5" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>press_release</t>
+          <t>40-F</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Company-issued press release</t>
+          <t>Canadian annual report</t>
         </is>
       </c>
     </row>
@@ -25377,12 +31766,12 @@
       <c r="A45" s="5" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>news_article</t>
+          <t>press_release</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Third-party news article</t>
+          <t>Company-issued press release</t>
         </is>
       </c>
     </row>
@@ -25390,12 +31779,12 @@
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>court_filing</t>
+          <t>news_article</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Direct court document</t>
+          <t>Third-party news article</t>
         </is>
       </c>
     </row>
@@ -25403,10 +31792,23 @@
       <c r="A47" s="5" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
+          <t>court_filing</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Direct court document</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>regulatory_notice</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Regulator-issued notice (SEC, EPA, ANM, etc.)</t>
         </is>
